--- a/reports/二级子公司D_利润表_2026-05.xlsx
+++ b/reports/二级子公司D_利润表_2026-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>88464391</v>
+        <v>90318911</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>86524937</v>
+        <v>86477645</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>400660226</v>
+        <v>401300751</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>298741</v>
+        <v>295665</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1382167</v>
+        <v>1383651</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>253893</v>
+        <v>253138</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1182585</v>
+        <v>1184864</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>211176</v>
+        <v>210924</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>986639</v>
+        <v>986338</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>191808</v>
+        <v>190009</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>889224</v>
+        <v>886823</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>106434</v>
+        <v>105752</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>493203</v>
+        <v>492311</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>84404</v>
+        <v>84802</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>394226</v>
+        <v>393703</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>87317935</v>
+        <v>89178621</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>85378481</v>
+        <v>85337355</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4771090</v>
+        <v>4799968</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>22178257</v>
+        <v>22177430</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>369169</v>
+        <v>373543</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1725775</v>
+        <v>1726700</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>638170</v>
+        <v>640050</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2963925</v>
+        <v>2963151</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>76760503</v>
+        <v>76694761</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>355286746</v>
+        <v>355887388</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1267716</v>
+        <v>1275484</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>5912689</v>
+        <v>5934675</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>422873</v>
+        <v>424099</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1974012</v>
+        <v>1978462</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2133237</v>
+        <v>2115418</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>9879422</v>
+        <v>9889119</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>531348</v>
+        <v>527865</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2465175</v>
+        <v>2470526</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1898241</v>
+        <v>1898392</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>8871866</v>
+        <v>8885248</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>41213</v>
+        <v>40959</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>206222</v>
+        <v>205948</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1140278</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>5320321</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>761637</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3544389</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>57987697</v>
+        <v>62169331</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>52064035</v>
+        <v>52094828</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>51114234</v>
+        <v>51134705</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>236769542</v>
+        <v>236382080</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>949801</v>
+        <v>960123</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>4434816</v>
+        <v>4436066</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1921069</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>8881434</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>614361</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2844993</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>383376</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1779603</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>459026</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2136572</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>343406</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1602527</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>228399</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1067945</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>189995</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>889284</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>898167</v>
+        <v>896411</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>4194212</v>
+        <v>4195223</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>693094</v>
+        <v>685607</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3210952</v>
+        <v>3204704</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>531660</v>
+        <v>528018</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2465471</v>
+        <v>2462835</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4007820</v>
+        <v>4020963</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>18727925</v>
+        <v>18705267</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>154451</v>
+        <v>159112</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>773251</v>
+        <v>738179</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>331564</v>
+        <v>330367</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1649331</v>
+        <v>1644042</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>370174</v>
+        <v>330367</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1851691</v>
+        <v>1644042</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>40978</v>
+        <v>41434</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>205920</v>
+        <v>205776</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>167857</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>834243</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>335926</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1556051</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111633</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>557213</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83533</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>418134</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>138872</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>696978</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>475700</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2224707</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>73772</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>371348</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55288</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>278246</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92175</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>463257</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64607</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>323969</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46244</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>231246</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>37087</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>184938</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27883</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>138721</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>29330238</v>
+        <v>28172823</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33612366</v>
+        <v>31320285</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>192095</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>888396</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46584</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>232003</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>71694</v>
+        <v>72335</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>360312</v>
+        <v>361191</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>29258544</v>
+        <v>28292583</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2586940</v>
+        <v>2570860</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>12875914</v>
+        <v>12906778</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>26671604</v>
+        <v>25721723</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>26671604</v>
+        <v>25721723</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>26671604</v>
+        <v>25721723</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>26671604</v>
+        <v>25721723</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>26671604</v>
+        <v>25721723</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
